--- a/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/antofagasta.xlsx
+++ b/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/antofagasta.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>70674.53999999999</v>
+        <v>70581.10000000001</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>22619.74</v>
+        <v>22718.57</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>87647.56</v>
+        <v>87043.44</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>56447.59</v>
+        <v>56556.21</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>12714.27</v>
+        <v>12739.84</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/antofagasta.xlsx
+++ b/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/antofagasta.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Antofagasta" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Antofagasta" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>957865-604-CM25</t>
+          <t>3834-69-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,12 +524,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>61.980.820-7</t>
+          <t>69.020.400-2</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE DERECHOS HUMANOS</t>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
+          <t>TOTALPACK LTDA.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>76.304.354-1</t>
+          <t>79.948.840-k</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>70581.10000000001</v>
+        <v>8655.459999999999</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1233623-15-CM26</t>
+          <t>812799-105-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,12 +585,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -600,12 +600,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>61.980.920-3</t>
+          <t>69.020.400-2</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Licancabur</t>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>VICTORIA SPA</t>
+          <t>TCHILECOM</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>76.188.587-1</t>
+          <t>77.349.120-8</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>22718.57</v>
+        <v>20687.61</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1233623-50-CM26</t>
+          <t>881-52-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,27 +646,27 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>61.980.920-3</t>
+          <t>72.224.100-2</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Licancabur</t>
+          <t>GOBIERNO REGIONAL DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>ANDESTIC SPA</t>
+          <t>Zecovery Ltda   -    EXEC</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>76.031.392-0</t>
+          <t>76.260.080-3</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>87043.44</v>
+        <v>38991.88</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2385-223-CM26</t>
+          <t>1233623-144-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,27 +707,27 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>69.020.200-K</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALAMA</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>VICTORIA SPA</t>
+          <t>VICTORIA SpA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>56556.21</v>
+        <v>29772.05</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>812799-115-CM26</t>
+          <t>1233623-153-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,27 +768,27 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>69.020.400-2</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>TCHILECOM</t>
+          <t>VICTORIA SpA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>77.349.120-8</t>
+          <t>76.188.587-1</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,7 +813,495 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
+        <v>383543.33</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2384-113-CM25</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>69.020.200-K</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>INGENIERIA Y SISTEMAS COMPUTACIONALES S.A.</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>79.560.740-4</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>671227.5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2429-2524-CM25</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>sep-2025</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>69.020.300-6</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Zecovery Ltda   -    EXEC</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>76.260.080-3</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>109466.65</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>957865-604-CM25</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>61.980.820-7</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>SUBSECRETARIA DE DERECHOS HUMANOS</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>76.304.354-1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>70581.10000000001</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>1233623-15-CM26</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>61.980.920-3</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Servicio Local de Educación Pública Licancabur</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>VICTORIA SPA</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>76.188.587-1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="n">
+        <v>22718.57</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>1233623-50-CM26</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>61.980.920-3</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Servicio Local de Educación Pública Licancabur</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ANDESTIC SPA</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>76.031.392-0</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="n">
+        <v>87043.44</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2385-223-CM26</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>69.020.200-K</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>VICTORIA SPA</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>76.188.587-1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="n">
+        <v>56556.21</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>812799-115-CM26</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>69.020.400-2</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>TCHILECOM</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>77.349.120-8</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="n">
         <v>12739.84</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>3506-625-CM26</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>69.020.100-3</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE TOCOPILLA</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>TICHILE  REVENTA  DE SOFTWARE Y HARDWARE SPA</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>76.334.381-2</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="n">
+        <v>7651.56</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/antofagasta.xlsx
+++ b/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/antofagasta.xlsx
@@ -941,7 +941,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>957865-604-CM25</t>
+          <t>1233623-15-CM26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -951,12 +951,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -966,12 +966,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>61.980.820-7</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE DERECHOS HUMANOS</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
+          <t>VICTORIA SpA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>76.304.354-1</t>
+          <t>76.188.587-1</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>70581.10000000001</v>
+        <v>22718.57</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1233623-15-CM26</t>
+          <t>1233623-50-CM26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1012,12 +1012,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>VICTORIA SPA</t>
+          <t>Andestic SpA</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>76.188.587-1</t>
+          <t>76.031.392-0</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>22718.57</v>
+        <v>87043.44</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1233623-50-CM26</t>
+          <t>2385-223-CM26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1073,12 +1073,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>61.980.920-3</t>
+          <t>69.020.200-K</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Licancabur</t>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>ANDESTIC SPA</t>
+          <t>VICTORIA SpA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>76.031.392-0</t>
+          <t>76.188.587-1</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>87043.44</v>
+        <v>56556.21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2385-223-CM26</t>
+          <t>812799-115-CM26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1134,12 +1134,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1149,12 +1149,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>69.020.200-K</t>
+          <t>69.020.400-2</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALAMA</t>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>VICTORIA SPA</t>
+          <t>TCHILECOM</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>76.188.587-1</t>
+          <t>77.349.120-8</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>56556.21</v>
+        <v>12739.84</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>812799-115-CM26</t>
+          <t>3506-625-CM26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1210,12 +1210,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>69.020.400-2</t>
+          <t>69.020.100-3</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+          <t>I MUNICIPALIDAD DE TOCOPILLA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>TCHILECOM</t>
+          <t>TICHILE  REVENTA  DE SOFTWARE Y HARDWARE SPA</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>77.349.120-8</t>
+          <t>76.334.381-2</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>12739.84</v>
+        <v>7651.56</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3506-625-CM26</t>
+          <t>1375735-48-CM26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>69.020.100-3</t>
+          <t>61.981.250-6</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TOCOPILLA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1286,12 +1286,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>TICHILE  REVENTA  DE SOFTWARE Y HARDWARE SPA</t>
+          <t>CONSULTORA, CHERRIE PIZARRO SANTOS EMPRESA INDIVIDUAL DE RESPONSABILID</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>76.334.381-2</t>
+          <t>76.522.707-0</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>7651.56</v>
+        <v>51168.17</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/antofagasta.xlsx
+++ b/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/antofagasta.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M14"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -684,7 +684,11 @@
           <t>76.260.080-3</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +749,11 @@
           <t>76.188.587-1</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +814,11 @@
           <t>76.188.587-1</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +940,11 @@
           <t>76.260.080-3</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1005,11 @@
           <t>76.188.587-1</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1131,11 @@
           <t>76.188.587-1</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1257,11 @@
           <t>76.334.381-2</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1302,6 +1330,71 @@
       </c>
       <c r="M14" s="2" t="n">
         <v>51168.17</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2429-1208-SE26</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>69.020.300-6</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Zecovery Ltda   -    EXEC</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>76.260.080-3</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="n">
+        <v>23439.34</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/antofagasta.xlsx
+++ b/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/antofagasta.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M15"/>
+  <dimension ref="A1:M17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1355,7 +1355,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1395,6 +1395,132 @@
       </c>
       <c r="M15" s="2" t="n">
         <v>23439.34</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>1261592-1364-CM26</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>71.102.600-2</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>ANALYZE CONSULTORIA Y DESARROLLO SPA</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>77.592.300-8</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="n">
+        <v>22571.56</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2258-7834-CM26</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>61.606.201-8</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Georg</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>76.624.276-6</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="n">
+        <v>11498.45</v>
       </c>
     </row>
   </sheetData>
